--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.06178998758998</v>
+        <v>1.960040872983372</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84473086981608</v>
+        <v>2.087268766345112</v>
       </c>
       <c r="E2" t="n">
-        <v>7.151282495099888</v>
+        <v>1.162083405453732</v>
       </c>
       <c r="F2" t="n">
-        <v>5.493065817174304</v>
+        <v>0.8926231952908245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.07047859059264</v>
+        <v>1.636452770971305</v>
       </c>
       <c r="D3" t="n">
-        <v>20.25490697088345</v>
+        <v>3.291422382768561</v>
       </c>
       <c r="E3" t="n">
-        <v>7.151282495099888</v>
+        <v>1.162083405453732</v>
       </c>
       <c r="F3" t="n">
-        <v>5.493065817174304</v>
+        <v>0.8926231952908245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.47090142347679</v>
+        <v>3.814021481314978</v>
       </c>
       <c r="D4" t="n">
-        <v>26.09493105717147</v>
+        <v>4.240426296790364</v>
       </c>
       <c r="E4" t="n">
-        <v>7.151282495099888</v>
+        <v>1.162083405453732</v>
       </c>
       <c r="F4" t="n">
-        <v>5.493065817174304</v>
+        <v>0.8926231952908245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.01756129177896</v>
+        <v>4.227853709914081</v>
       </c>
       <c r="D5" t="n">
-        <v>25.84249988886224</v>
+        <v>4.199406231940114</v>
       </c>
       <c r="E5" t="n">
-        <v>7.151282495099888</v>
+        <v>1.162083405453732</v>
       </c>
       <c r="F5" t="n">
-        <v>5.493065817174304</v>
+        <v>0.8926231952908245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.68989043850852</v>
+        <v>2.712107196257635</v>
       </c>
       <c r="D6" t="n">
-        <v>19.18855826272881</v>
+        <v>3.118140717693432</v>
       </c>
       <c r="E6" t="n">
-        <v>7.151282495099888</v>
+        <v>1.162083405453732</v>
       </c>
       <c r="F6" t="n">
-        <v>5.493065817174304</v>
+        <v>0.8926231952908245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.32477042445415</v>
+        <v>4.765275193973799</v>
       </c>
       <c r="D7" t="n">
-        <v>29.42949744967957</v>
+        <v>4.78229333557293</v>
       </c>
       <c r="E7" t="n">
-        <v>7.151282495099888</v>
+        <v>1.162083405453732</v>
       </c>
       <c r="F7" t="n">
-        <v>5.493065817174304</v>
+        <v>0.8926231952908245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
